--- a/data/therapy.xlsx
+++ b/data/therapy.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V3 final + 치료센터\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V5 -\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,582 +19,587 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="192">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="193">
+  <x:si>
+    <x:t>언어, 미술, 놀이, 인지, 음악, 행동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 인지. 미술, 감통, 행동재활</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 사회성발달집단놀이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 행동, 인지, 미술, 감통</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 154, 4층 (반도프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 미술, 청각장애 청능훈련</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 인지, 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 미술, 놀이, 심리, 인지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 능곡번영길 24 , 6층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 감통, 인지, 특수체육,  행동, 심리, 운동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 목감둘레로 253-35 목감예스프라자 24, 602~604호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 감통, 놀이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타방과후(주간보호)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미술, 음악, 인지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타(학생 피아노)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물리, 작업, 언어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인천</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧</x:t>
+  </x:si>
+  <x:si>
+    <x:t>_</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 인지, 감통, 놀이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-314-0660</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심리, 운동재활, 특수체육</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타방과후( 피트니스)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 인지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 서울대학로 264번길 26-32, 5층 (배곧중앙프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 운동, 감통, 인지, 심리, 심리운동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 감통, 음악, 인지, 특수체육, 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 서울대학로 278번길 61, 4층 (배곧 베니스스퀘어)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 157,  301~303호 (은행동, 호정빌딩)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 감통, 인지, 기타, 운동, 특수체육</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인천 연수구 테크노파크로 111번길 8, 4층 (송도 S타워)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 서울대학로 264번길  44-4 (에스프라자 508호)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 승지로 58,  401~402호 (능곡동, 태영프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 승지로 60번길 12, 5층 (광장프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧3로 80, 307호 (센터프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계중앙로 374, 304호 (골든웨이2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 감통, 미술, 인지, 심리운동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 감통, 인지, 행동, 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 장현능곡로 15,  401호 (승호프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계로 260, 501호 (우평라비엔빌딩)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계번영길 7, 403호 (단디프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 음악, 감통, 미술, 인지, 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계중앙로 374, 404호 (골든웨이2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-432-4275</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-3577</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-318-8863</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-311-8278</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-434-8040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유란아동청소년심리발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7008-8783</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 미술, 놀이, 음악, 감통, 심리운동</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">마음그린 언어심리센터 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 서울대학로 264번길 44-4, 9층 (에스프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-403-0110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빛누리장애인주간보호시설</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-362-5935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-3372</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이해공감언어심리발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-434-3373</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-496-4666</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">함현상생종합사회복지관 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 목감초등길 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 심리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>032-435-6735</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-431-1714</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-311-7583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>032-466-0610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-7552</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밝은아이아동발달센터_대야점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-316-2103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-435-2060</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-311-1223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-7009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-8253-0101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 함송로 29번길 67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-498-4690</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-319-6195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-435-7579</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-402-4512</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밝은아이아동발달센터_정왕점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-498-6255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-4129-2760</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰돌이언어청각발달연구소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-5352</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">시흥시정왕종합사회복지관 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-0077</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인천 남동구 장승로 32, 6층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-9112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-499-4004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-8560</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-432-7583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-435-0481</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-411-7945</x:t>
+  </x:si>
+  <x:si>
+    <x:t>032-715-6567</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 18, 에이플러스 403-5호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-497-9370</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-506-5505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마음CC발달심리상담센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>032-461-5242</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">마음나무 심리상담센터 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도장애인재활협회ㅡ시흥지부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 정왕대로 230, 409호 (정왕동, 제일프라자)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 장곡동 3025-1 대광프라자 501-504호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 시청로68번길 14 (장현동, 주호빌딩 2층)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 미술, 놀이, 인지, 작업, 감통, 특수체육</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인천광역시 남동구 서창남순환로 216번길 20, 505호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-311-7797</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밝은아이아동발달센터_능곡점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키즈드림 소아청소년과의원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위드아이아동발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 감통</x:t>
+  </x:si>
+  <x:si>
+    <x:t>봄 심리발달상담센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공감심리상담센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥목감종합사회복지관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 미술, 놀이</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">유얼리발달센터 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>허그맘허그인 시흥센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥이루다운동발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너나우리발달심리센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>톰소여 언어발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥ABA발달연구소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어발달연구소 별하</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크는아이발달지원센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이비소아청소년과의원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하나린심리언어발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계연세365의원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박동원재활의학과의원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은계중앙로 306번길 69, 404호</x:t>
+  </x:si>
   <x:si>
     <x:t>배곧아동발달센터</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">목감아동발달센터 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 호현로 55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미래아동청소년발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 심리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바른마음행동발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">아이맘ABA발달센터 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥대야종합사회복지관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키블아동발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">아이나래아동발달센터 </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">시흥장애인종합복지관 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>위드영심리상담센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계아동청소년발달센터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아람ABA발달연구소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행동, 특수체육</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 정왕대로 233번길 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 정왕대로 233번길 27-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 18, 205호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-313-2556</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">다지기아동발달센터_시흥점 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-404-8112</x:t>
+  </x:si>
+  <x:si>
     <x:t>032-437-6677</x:t>
   </x:si>
   <x:si>
-    <x:t>031-435-2060</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-314-0660</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-7552</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-431-1714</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕</x:t>
+    <x:t>031-504-0511</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 행동, 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 감통, 인지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
   </x:si>
   <x:si>
     <x:t>연락처</x:t>
   </x:si>
   <x:si>
-    <x:t>지역구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분야</x:t>
+    <x:t>주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어</x:t>
   </x:si>
   <x:si>
     <x:t>기관명</x:t>
   </x:si>
   <x:si>
-    <x:t>소래</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-316-2103</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">마음그린 언어심리센터 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-311-8278</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-506-5505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-8560</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-402-4512</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">다지기아동발달센터_시흥점 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도장애인재활협회ㅡ시흥지부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-498-6255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-3577</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빛누리장애인주간보호시설</x:t>
-  </x:si>
-  <x:si>
-    <x:t>032-466-0610</x:t>
-  </x:si>
-  <x:si>
-    <x:t>032-435-6735</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-497-9370</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키즈드림 소아청소년과의원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-2556</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-499-4004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-496-4666</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">함현상생종합사회복지관 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 인지, 감통, 놀이</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시흥시정왕종합사회복지관 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>032-715-6567</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-432-7583</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 목감초등길 45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 함송로 29번길 67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 운동, 감통, 인지, 심리, 심리운동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 157,  301~303호 (은행동, 호정빌딩)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 승지로 58,  401~402호 (능곡동, 태영프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 서울대학로 264번길 44-4, 9층 (에스프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 서울대학로 264번길  44-4 (에스프라자 508호)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 감통, 인지, 기타, 운동, 특수체육</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 감통, 음악, 인지, 특수체육, 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 서울대학로 278번길 61, 4층 (배곧 베니스스퀘어)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 서울대학로 264번길 26-32, 5층 (배곧중앙프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인천 연수구 테크노파크로 111번길 8, 4층 (송도 S타워)</x:t>
+    <x:t>놀이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 정왕대로 220 우리빌딩 5층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 음악, 운동, 감통, 심리운동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 진말1로 18, 에스엠타워 4층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행고길 28, 웃터골파크 3층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 81-52, 303호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 은행로 86 경동프라자 304호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 99, 로얄페스타 301호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 인지, 놀이, 미술, 감통, 작업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 미술, 감통, 심리운동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 하중로 193, 503~504호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>언어, 놀이, 인지, 감통, 기타(사회성그룹)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>놀이, 미술</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하나더하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마음공감플러스</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">느티숲 </x:t>
   </x:si>
   <x:si>
     <x:t>시흥시 능곡로 승지로 54,  3층 303~304호 (능곡동,  한일프라자)</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">아이맘ABA발달센터 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>아람ABA발달연구소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행동, 특수체육</x:t>
-  </x:si>
-  <x:si>
-    <x:t>톰소여 언어발달센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥이루다운동발달센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타방과후(주간보호)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>박동원재활의학과의원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허그맘허그인 시흥센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공감심리상담센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위드아이아동발달센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 감통, 놀이</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">유얼리발달센터 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>크는아이발달지원센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위드영심리상담센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미술, 음악, 인지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이비소아청소년과의원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키블아동발달센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너나우리발달심리센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 미술, 놀이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물리, 작업, 언어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>봄 심리발달상담센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어발달연구소 별하</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 심리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥ABA발달연구소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하나린심리언어발달센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥대야종합사회복지관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계연세365의원</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">목감아동발달센터 </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">시흥장애인종합복지관 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>미래아동청소년발달센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하나더하기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>놀이, 미술</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마음공감플러스</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">느티숲 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-404-8112</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-3372</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-8253-0101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰돌이언어청각발달연구소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-0077</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-411-7945</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-498-4690</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밝은아이아동발달센터_능곡점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7008-8783</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이해공감언어심리발달센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-5352</x:t>
-  </x:si>
-  <x:si>
-    <x:t>032-461-5242</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밝은아이아동발달센터_정왕점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밝은아이아동발달센터_대야점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타방과후( 피트니스)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-318-8863</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유란아동청소년심리발달센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 인지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마음CC발달심리상담센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-311-7797</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-403-0110</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-9112</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-311-7583</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-8040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 호현로 55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계아동청소년발달센터</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">아이나래아동발달센터 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 감통</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인천 남동구 장승로 32, 6층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 능곡번영길 24 , 6층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 18, 205호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 인지, 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 미술, 놀이, 심리, 인지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 정왕대로 233번길 27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 행동, 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 미술, 청각장애 청능훈련</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 정왕대로 233번길 27-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 감통, 인지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 미술, 놀이, 음악, 감통, 심리운동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계중앙로 374, 304호 (골든웨이2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 감통, 인지, 행동, 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 승지로 60번길 12, 5층 (광장프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계번영길 7, 403호 (단디프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 음악, 감통, 미술, 인지, 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계중앙로 306번길 69, 404호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계중앙로 374, 404호 (골든웨이2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은계로 260, 501호 (우평라비엔빌딩)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 감통, 미술, 인지, 심리운동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 18, 에이플러스 403-5호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 장현능곡로 15,  401호 (승호프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧3로 80, 307호 (센터프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 인지, 감통, 기타(사회성그룹)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-435-7579</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 심리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-319-6195</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-3373</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-4129-2760</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">마음나무 심리상담센터 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-435-0481</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-311-1223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-362-5935</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 감통, 인지, 특수체육,  행동, 심리, 운동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 목감둘레로 253-35 목감예스프라자 24, 602~604호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-432-4275</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-7009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-504-0511</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심리, 운동재활, 특수체육</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 사회성발달집단놀이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 진말1로 18, 에스엠타워 4층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 정왕대로 220 우리빌딩 5층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 행동, 인지, 미술, 감통</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 놀이, 미술, 감통, 심리운동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 154, 4층 (반도프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 99, 로얄페스타 301호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행로 86 경동프라자 304호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 81-52, 303호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 음악, 운동, 감통, 심리운동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 인지, 놀이, 미술, 감통, 작업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 미술, 놀이, 인지, 음악, 행동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 은행고길 28, 웃터골파크 3층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 인지. 미술, 감통, 행동재활</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 하중로 193, 503~504호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인천</x:t>
-  </x:si>
-  <x:si>
-    <x:t>놀이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>_</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥목감종합사회복지관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타(학생 피아노)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>바른마음행동발달센터</x:t>
+    <x:t>시흥시 수풀안길 14-23, 201호 (메트로타워2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 중심상가 4길 10-1 , 402호 (정원빌딩)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인천 남동구 남동대로 893, 301호 (루카이스타워)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 비둘기공원 7길 33,  205호 (디아망타운)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 배곧4로 30, 401호 (정왕동, 배곧타운1)</x:t>
   </x:si>
   <x:si>
     <x:t>인천광역시 남동구 장승남로 38,  반달프라자 302호</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥시 비둘기공원 7길 33,  205호 (디아망타운)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 중심상가 4길 10-1 , 402호 (정원빌딩)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인천광역시 남동구 서창남순환로 216번길 20, 505호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 수풀안길 14-23, 201호 (메트로타워2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 정왕대로 230, 409호 (정왕동, 제일프라자)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인천 남동구 남동대로 893, 301호 (루카이스타워)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 시청로68번길 14 (장현동, 주호빌딩 2층)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 배곧4로 30, 401호 (정왕동, 배곧타운1)</x:t>
+    <x:t>언어, 놀이, 미술, 감통, 인지, 청각장애 청능훈련</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥시 목감우회로 39, 208호 (목감 시티프라자)</x:t>
   </x:si>
   <x:si>
     <x:t>인천광역시 남동구 앵고개로 847번길 80-1, 307호</x:t>
   </x:si>
   <x:si>
-    <x:t>언어, 놀이, 미술, 감통, 인지, 청각장애 청능훈련</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 장곡동 3025-1 대광프라자 501-504호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>언어, 미술, 놀이, 인지, 작업, 감통, 특수체육</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥시 목감우회로 39, 208호 (목감 시티프라자)</x:t>
+    <x:r>
+      <x:t>37.377921</x:t>
+    </x:r>
   </x:si>
 </x:sst>
 </file>
@@ -632,16 +637,46 @@
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff6482f0"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff6482f0"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff6482f0"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
   <x:fills count="3">
     <x:fill>
@@ -835,8 +870,8 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <x:cellXfs count="29">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1080,10 +1115,13 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <x:cellStyle name="표준" xfId="1" builtinId="0" iLevel="0"/>
+    <x:cellStyle name="표준" xfId="1"/>
   </x:cellStyles>
   <x:dxfs/>
   <x:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1386,42 +1424,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" t="s">
-        <x:v>11</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>15</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>7</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>17</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>9</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7" ht="32.75">
       <x:c r="A2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B2" s="21" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C2" s="10" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D2" s="10" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F2">
         <x:v>37.444887943136798</x:v>
@@ -1432,19 +1470,19 @@
     </x:row>
     <x:row r="3" spans="1:7" ht="32.75">
       <x:c r="A3" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B3" s="21" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="10" t="s">
-        <x:v>132</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D3" s="10" t="s">
-        <x:v>161</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F3">
         <x:v>37.444752003045103</x:v>
@@ -1455,19 +1493,19 @@
     </x:row>
     <x:row r="4" spans="1:7" ht="32.75">
       <x:c r="A4" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B4" s="21" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="10" t="s">
-        <x:v>126</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>179</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F4">
         <x:v>37.443015045209002</x:v>
@@ -1478,19 +1516,19 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="32.75">
       <x:c r="A5" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B5" s="21" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="10" t="s">
-        <x:v>136</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>163</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F5">
         <x:v>37.439255254876898</x:v>
@@ -1501,19 +1539,19 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="32.75">
       <x:c r="A6" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="10" t="s">
-        <x:v>159</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E6" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F6">
         <x:v>37.452025078338103</x:v>
@@ -1524,19 +1562,19 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="3" t="s">
-        <x:v>105</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="22" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>72</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>134</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>147</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F7">
         <x:v>37.450928848036398</x:v>
@@ -1547,19 +1585,19 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B8" s="22" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C8" s="16" t="s">
-        <x:v>124</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D8" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F8">
         <x:v>37.444817461772402</x:v>
@@ -1570,19 +1608,19 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B9" s="22" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="16" t="s">
-        <x:v>127</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E9" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F9">
         <x:v>37.4370981790032</x:v>
@@ -1593,19 +1631,19 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="3" t="s">
-        <x:v>177</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B10" s="22" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="16" t="s">
-        <x:v>165</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D10" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E10" s="9" t="s">
-        <x:v>174</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F10">
         <x:v>37.450928848036398</x:v>
@@ -1616,19 +1654,19 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B11" s="22" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C11" s="16" t="s">
-        <x:v>166</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D11" s="11" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F11">
         <x:v>37.440757219133197</x:v>
@@ -1639,19 +1677,19 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="3" t="s">
-        <x:v>79</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B12" s="22" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
-        <x:v>86</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D12" s="11" t="s">
-        <x:v>113</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E12" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F12">
         <x:v>37.445536329493002</x:v>
@@ -1662,19 +1700,19 @@
     </x:row>
     <x:row r="13" spans="1:7" ht="32.75">
       <x:c r="A13" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B13" s="21" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="10" t="s">
-        <x:v>120</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D13" s="10" t="s">
-        <x:v>47</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F13">
         <x:v>37.367175821953602</x:v>
@@ -1685,19 +1723,19 @@
     </x:row>
     <x:row r="14" spans="1:7" ht="32.75">
       <x:c r="A14" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B14" s="21" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="10" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D14" s="10" t="s">
-        <x:v>162</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E14" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F14">
         <x:v>37.374066672514303</x:v>
@@ -1708,19 +1746,19 @@
     </x:row>
     <x:row r="15" spans="1:7" ht="32.75">
       <x:c r="A15" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B15" s="21" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="10" t="s">
-        <x:v>167</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="10" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E15" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F15">
         <x:v>37.377342450217498</x:v>
@@ -1731,19 +1769,19 @@
     </x:row>
     <x:row r="16" spans="1:7" ht="32.75">
       <x:c r="A16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B16" s="21" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="10" t="s">
-        <x:v>126</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
-        <x:v>137</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F16">
         <x:v>37.377920607306599</x:v>
@@ -1754,22 +1792,22 @@
     </x:row>
     <x:row r="17" spans="1:7" ht="32.75">
       <x:c r="A17" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B17" s="23" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D17" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E17" s="4" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F17">
-        <x:v>126.72646885066899</x:v>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F17" s="28" t="s">
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G17">
         <x:v>126.72646885066899</x:v>
@@ -1777,19 +1815,19 @@
     </x:row>
     <x:row r="18" spans="1:7" ht="32.75">
       <x:c r="A18" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B18" s="21" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="10" t="s">
-        <x:v>121</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F18">
         <x:v>37.374954691815503</x:v>
@@ -1800,19 +1838,19 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B19" s="24" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C19" s="17" t="s">
-        <x:v>190</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D19" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E19" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F19">
         <x:v>37.367175821953602</x:v>
@@ -1823,19 +1861,19 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B20" s="22" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>84</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D20" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F20">
         <x:v>37.366609268772599</x:v>
@@ -1846,19 +1884,19 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B21" s="22" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="16" t="s">
-        <x:v>142</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D21" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F21">
         <x:v>37.368185599029196</x:v>
@@ -1869,19 +1907,19 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="3" t="s">
-        <x:v>75</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B22" s="22" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
         <x:v>116</x:v>
       </x:c>
       <x:c r="D22" s="11" t="s">
-        <x:v>139</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E22" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F22">
         <x:v>37.370521385466503</x:v>
@@ -1892,19 +1930,19 @@
     </x:row>
     <x:row r="23" spans="1:7" ht="32.75">
       <x:c r="A23" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="21" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C23" s="10" t="s">
-        <x:v>48</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D23" s="10" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F23">
         <x:v>37.369024035891698</x:v>
@@ -1915,19 +1953,19 @@
     </x:row>
     <x:row r="24" spans="1:7" ht="32.75">
       <x:c r="A24" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B24" s="21" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C24" s="10" t="s">
-        <x:v>150</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D24" s="10" t="s">
-        <x:v>53</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E24" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F24">
         <x:v>37.3687471</x:v>
@@ -1938,19 +1976,19 @@
     </x:row>
     <x:row r="25" spans="1:7" ht="32.75">
       <x:c r="A25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B25" s="21" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C25" s="10" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D25" s="10" t="s">
-        <x:v>185</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F25">
         <x:v>37.381306954340303</x:v>
@@ -1961,19 +1999,19 @@
     </x:row>
     <x:row r="26" spans="1:7" ht="32.75">
       <x:c r="A26" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B26" s="21" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>103</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D26" s="14" t="s">
-        <x:v>170</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E26" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F26">
         <x:v>37.394423320013097</x:v>
@@ -1984,19 +2022,19 @@
     </x:row>
     <x:row r="27" spans="1:7" ht="32.75">
       <x:c r="A27" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B27" s="21" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D27" s="10" t="s">
-        <x:v>157</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E27" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F27">
         <x:v>37.377816391155001</x:v>
@@ -2007,19 +2045,19 @@
     </x:row>
     <x:row r="28" spans="1:7" ht="32.75">
       <x:c r="A28" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B28" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C28" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E28" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F28">
         <x:v>37.370079914105503</x:v>
@@ -2030,19 +2068,19 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="6" t="s">
-        <x:v>98</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B29" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C29" s="18" t="s">
         <x:v>116</x:v>
       </x:c>
       <x:c r="D29" s="11" t="s">
-        <x:v>138</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E29" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F29">
         <x:v>37.3729966283152</x:v>
@@ -2053,19 +2091,19 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B30" s="22" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C30" s="16" t="s">
-        <x:v>56</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D30" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E30" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F30">
         <x:v>37.368462683805397</x:v>
@@ -2076,19 +2114,19 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B31" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C31" s="17" t="s">
-        <x:v>140</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D31" s="13" t="s">
-        <x:v>189</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E31" s="5" t="s">
-        <x:v>108</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F31">
         <x:v>37.382521199999999</x:v>
@@ -2099,19 +2137,19 @@
     </x:row>
     <x:row r="32" spans="1:7" ht="32.75">
       <x:c r="A32" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B32" s="21" t="s">
-        <x:v>6</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C32" s="10" t="s">
-        <x:v>73</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D32" s="10" t="s">
-        <x:v>158</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E32" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F32">
         <x:v>37.345491655756803</x:v>
@@ -2122,19 +2160,19 @@
     </x:row>
     <x:row r="33" spans="1:7" ht="32.75">
       <x:c r="A33" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B33" s="21" t="s">
-        <x:v>6</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C33" s="10" t="s">
-        <x:v>106</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D33" s="10" t="s">
-        <x:v>180</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E33" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F33">
         <x:v>37.344352855221899</x:v>
@@ -2145,19 +2183,19 @@
     </x:row>
     <x:row r="34" spans="1:7" ht="32.75">
       <x:c r="A34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B34" s="21" t="s">
-        <x:v>6</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C34" s="10" t="s">
-        <x:v>68</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="10" t="s">
-        <x:v>125</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E34" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F34">
         <x:v>37.347664695671803</x:v>
@@ -2168,19 +2206,19 @@
     </x:row>
     <x:row r="35" spans="1:7" ht="32.75">
       <x:c r="A35" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B35" s="21" t="s">
-        <x:v>6</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C35" s="10" t="s">
-        <x:v>129</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D35" s="10" t="s">
-        <x:v>183</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E35" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F35">
         <x:v>37.344967088785999</x:v>
@@ -2191,19 +2229,19 @@
     </x:row>
     <x:row r="36" spans="1:7" ht="32.75">
       <x:c r="A36" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B36" s="21" t="s">
-        <x:v>6</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C36" s="10" t="s">
-        <x:v>156</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D36" s="10" t="s">
-        <x:v>122</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E36" s="2" t="s">
-        <x:v>143</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F36">
         <x:v>37.347376152578597</x:v>
@@ -2214,19 +2252,19 @@
     </x:row>
     <x:row r="37" spans="1:7" ht="32.75">
       <x:c r="A37" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B37" s="21" t="s">
-        <x:v>6</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C37" s="10" t="s">
-        <x:v>123</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D37" s="10" t="s">
-        <x:v>42</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E37" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F37">
         <x:v>37.364263604049299</x:v>
@@ -2237,19 +2275,19 @@
     </x:row>
     <x:row r="38" spans="1:7" ht="32.75">
       <x:c r="A38" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B38" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C38" s="10" t="s">
-        <x:v>126</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D38" s="10" t="s">
-        <x:v>151</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E38" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F38">
         <x:v>37.380980220629297</x:v>
@@ -2260,19 +2298,19 @@
     </x:row>
     <x:row r="39" spans="1:7" ht="32.75">
       <x:c r="A39" s="2" t="s">
-        <x:v>175</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B39" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C39" s="10" t="s">
-        <x:v>176</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D39" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E39" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F39">
         <x:v>37.385644748707001</x:v>
@@ -2283,19 +2321,19 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B40" s="22" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C40" s="16" t="s">
-        <x:v>76</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D40" s="11" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E40" s="3" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F40">
         <x:v>37.3818990219157</x:v>
@@ -2306,19 +2344,19 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B41" s="24" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C41" s="17" t="s">
-        <x:v>86</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D41" s="13" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E41" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F41">
         <x:v>37.381119519899002</x:v>
@@ -2329,19 +2367,19 @@
     </x:row>
     <x:row r="42" spans="1:7" ht="32.75">
       <x:c r="A42" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B42" s="23" t="s">
-        <x:v>171</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C42" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E42" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F42">
         <x:v>37.445203605811898</x:v>
@@ -2352,19 +2390,19 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B43" s="22" t="s">
-        <x:v>171</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="16" t="s">
-        <x:v>173</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D43" s="11" t="s">
-        <x:v>52</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E43" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F43">
         <x:v>37.385873089543203</x:v>
@@ -2375,19 +2413,19 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="7" t="s">
-        <x:v>83</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B44" s="26" t="s">
-        <x:v>171</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C44" s="19" t="s">
-        <x:v>173</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D44" s="13" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E44" s="7" t="s">
-        <x:v>1</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F44">
         <x:v>37.462077408961697</x:v>
@@ -2398,19 +2436,19 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B45" s="22" t="s">
-        <x:v>171</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C45" s="16" t="s">
-        <x:v>169</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D45" s="11" t="s">
-        <x:v>187</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E45" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F45">
         <x:v>37.398905068168602</x:v>
@@ -2421,19 +2459,19 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="3" t="s">
-        <x:v>71</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B46" s="22" t="s">
-        <x:v>171</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C46" s="16" t="s">
-        <x:v>172</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D46" s="11" t="s">
-        <x:v>178</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E46" s="3" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F46">
         <x:v>37.443155395163402</x:v>
@@ -2444,19 +2482,19 @@
     </x:row>
     <x:row r="47" spans="1:7" ht="16.75">
       <x:c r="A47" s="8" t="s">
-        <x:v>57</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B47" s="27" t="s">
-        <x:v>171</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C47" s="20" t="s">
-        <x:v>160</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D47" s="15" t="s">
-        <x:v>181</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E47" s="8" t="s">
-        <x:v>29</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F47">
         <x:v>37.423204016787601</x:v>
@@ -2466,7 +2504,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104492" right="0.69999998807907104492" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
